--- a/cnk_item_addon.xlsx
+++ b/cnk_item_addon.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="58">
   <si>
     <t>Settings</t>
   </si>
@@ -87,6 +87,9 @@
     <t>Ages</t>
   </si>
   <si>
+    <t>Custom Station Proccess</t>
+  </si>
+  <si>
     <t>spiced</t>
   </si>
   <si>
@@ -130,6 +133,9 @@
   </si>
   <si>
     <t>spiced.basil</t>
+  </si>
+  <si>
+    <t>mash</t>
   </si>
   <si>
     <t>diced_onion</t>
@@ -227,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -239,6 +245,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -467,6 +476,7 @@
     <col customWidth="1" min="11" max="11" width="16.0"/>
     <col customWidth="1" min="12" max="12" width="15.5"/>
     <col customWidth="1" min="14" max="14" width="13.5"/>
+    <col customWidth="1" min="18" max="18" width="20.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -500,55 +510,57 @@
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1"/>
-    <row r="5" ht="15.75" customHeight="1"/>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="B5" s="4"/>
+    </row>
     <row r="6" ht="15.75" customHeight="1"/>
     <row r="7" ht="15.75" customHeight="1"/>
     <row r="8" ht="15.75" customHeight="1"/>
     <row r="9" ht="15.75" customHeight="1"/>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="O10" s="5" t="s">
         <v>20</v>
       </c>
       <c r="P10" s="1" t="s">
@@ -557,192 +569,198 @@
       <c r="Q10" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="R10" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>1.0</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="4">
+      <c r="E11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="5">
         <v>1.0</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="5">
         <v>0.0</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>27</v>
+      <c r="H11" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="4">
+      <c r="A12" s="5">
         <v>2.0</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="B12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="J12" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="K12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="L12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="N12" s="4" t="s">
+      <c r="M12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="O12" s="4" t="s">
+      <c r="N12" s="5" t="s">
         <v>37</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="4">
+      <c r="A13" s="5">
         <v>3.0</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="B13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="5">
         <v>1.0</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="5">
         <v>1.0</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>41</v>
+      <c r="H13" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="4">
+      <c r="A14" s="5">
         <v>4.0</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="B14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="5">
         <v>10.0</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="5">
         <v>14.0</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K14" s="4" t="s">
+      <c r="H14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="J14" s="5" t="s">
         <v>47</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="4">
+      <c r="A15" s="5">
         <v>5.0</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="B15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="5">
         <v>0.0</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="5">
         <v>0.0</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J15" s="4" t="s">
+      <c r="H15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="I15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="J15" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="K15" s="5" t="s">
         <v>55</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="P15" s="1">
         <v>0.0</v>

--- a/cnk_item_addon.xlsx
+++ b/cnk_item_addon.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="60">
   <si>
     <t>Settings</t>
   </si>
@@ -90,6 +90,9 @@
     <t>Custom Station Proccess</t>
   </si>
   <si>
+    <t>Distill TIme</t>
+  </si>
+  <si>
     <t>spiced</t>
   </si>
   <si>
@@ -190,6 +193,9 @@
   </si>
   <si>
     <t>cnk.cooking_oil</t>
+  </si>
+  <si>
+    <t>15s</t>
   </si>
 </sst>
 </file>
@@ -572,22 +578,25 @@
       <c r="R10" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="S10" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="6">
         <v>1.0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11" s="5">
         <v>1.0</v>
@@ -596,7 +605,7 @@
         <v>0.0</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
@@ -604,16 +613,16 @@
         <v>2.0</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="5">
         <v>0.0</v>
@@ -622,31 +631,31 @@
         <v>0.5</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
@@ -654,16 +663,16 @@
         <v>3.0</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" s="5">
         <v>1.0</v>
@@ -672,16 +681,16 @@
         <v>1.0</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
@@ -689,16 +698,16 @@
         <v>4.0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F14" s="5">
         <v>10.0</v>
@@ -707,19 +716,19 @@
         <v>14.0</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
@@ -727,16 +736,16 @@
         <v>5.0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" s="5">
         <v>0.0</v>
@@ -745,28 +754,31 @@
         <v>0.0</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P15" s="1">
         <v>0.0</v>
       </c>
       <c r="Q15" s="1" t="b">
         <v>0</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
